--- a/donnees-fictives/Dépenses fictives - inventaire v7.xlsx
+++ b/donnees-fictives/Dépenses fictives - inventaire v7.xlsx
@@ -2488,7 +2488,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2497,14 +2497,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>BOUCHERIE DU MARCHE VILLE</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-80.63</v>
+        <v>-19.16</v>
       </c>
       <c r="F22" t="n">
-        <v>80.63</v>
+        <v>19.16</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2537,7 +2537,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2546,23 +2546,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-80.04000000000001</v>
+        <v>-80.63</v>
       </c>
       <c r="F23" t="n">
-        <v>80.04000000000001</v>
+        <v>80.63</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2580,13 +2580,13 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46053</v>
+        <v>46051</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2595,23 +2595,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PRIMEUR DE LA PLACE VILLE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-6.98</v>
+        <v>-80.04000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>6.98</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2629,13 +2629,13 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2644,14 +2644,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>PRIMEUR DE LA PLACE VILLE</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-45.82</v>
+        <v>-6.98</v>
       </c>
       <c r="F25" t="n">
-        <v>45.82</v>
+        <v>6.98</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="P25" s="1" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-112.03</v>
+        <v>-45.82</v>
       </c>
       <c r="F26" t="n">
-        <v>112.03</v>
+        <v>45.82</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-76.88</v>
+        <v>-112.03</v>
       </c>
       <c r="F27" t="n">
-        <v>76.88</v>
+        <v>112.03</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2791,23 +2791,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-28.76</v>
+        <v>-76.88</v>
       </c>
       <c r="F28" t="n">
-        <v>28.76</v>
+        <v>76.88</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2840,23 +2840,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-8.210000000000001</v>
+        <v>-28.76</v>
       </c>
       <c r="F29" t="n">
-        <v>8.210000000000001</v>
+        <v>28.76</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2880,7 +2880,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46058</v>
+        <v>46055</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2889,23 +2889,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-30.7</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>30.7</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2929,7 +2929,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-15.51</v>
+        <v>-30.7</v>
       </c>
       <c r="F31" t="n">
-        <v>15.51</v>
+        <v>30.7</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46060</v>
+        <v>46059</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2987,14 +2987,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-116.95</v>
+        <v>-15.51</v>
       </c>
       <c r="F32" t="n">
-        <v>116.95</v>
+        <v>15.51</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3036,14 +3036,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-110.38</v>
+        <v>-116.95</v>
       </c>
       <c r="F33" t="n">
-        <v>110.38</v>
+        <v>116.95</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3070,13 +3070,13 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46062</v>
+        <v>46060</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3085,23 +3085,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-23.72</v>
+        <v>-110.38</v>
       </c>
       <c r="F34" t="n">
-        <v>23.72</v>
+        <v>110.38</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3119,13 +3119,13 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3134,23 +3134,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-32.94</v>
+        <v>-23.72</v>
       </c>
       <c r="F35" t="n">
-        <v>32.94</v>
+        <v>23.72</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3183,23 +3183,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-19.1</v>
+        <v>-32.94</v>
       </c>
       <c r="F36" t="n">
-        <v>19.1</v>
+        <v>32.94</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3223,7 +3223,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46067</v>
+        <v>46063</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3232,23 +3232,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-133.36</v>
+        <v>-19.1</v>
       </c>
       <c r="F37" t="n">
-        <v>133.36</v>
+        <v>19.1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3266,13 +3266,13 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46068</v>
+        <v>46067</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-141.41</v>
+        <v>-133.36</v>
       </c>
       <c r="F38" t="n">
-        <v>141.41</v>
+        <v>133.36</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3330,14 +3330,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PRIMEUR DE LA PLACE VILLE</t>
+          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-11.95</v>
+        <v>-141.41</v>
       </c>
       <c r="F39" t="n">
-        <v>11.95</v>
+        <v>141.41</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3364,13 +3364,13 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46071</v>
+        <v>46068</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3379,14 +3379,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>PRIMEUR DE LA PLACE VILLE</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-10.76</v>
+        <v>-11.95</v>
       </c>
       <c r="F40" t="n">
-        <v>10.76</v>
+        <v>11.95</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3428,14 +3428,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-35.6</v>
+        <v>-10.76</v>
       </c>
       <c r="F41" t="n">
-        <v>35.6</v>
+        <v>10.76</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3468,7 +3468,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3477,23 +3477,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-13.21</v>
+        <v>-35.6</v>
       </c>
       <c r="F42" t="n">
-        <v>13.21</v>
+        <v>35.6</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3517,7 +3517,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46078</v>
+        <v>46073</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3526,23 +3526,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-106.34</v>
+        <v>-13.21</v>
       </c>
       <c r="F43" t="n">
-        <v>106.34</v>
+        <v>13.21</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3575,14 +3575,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-29.22</v>
+        <v>-106.34</v>
       </c>
       <c r="F44" t="n">
-        <v>29.22</v>
+        <v>106.34</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4301,7 +4301,7 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>-8.039999999999999</v>
+        <v>-12.92</v>
       </c>
       <c r="F59" t="n">
-        <v>8.039999999999999</v>
+        <v>12.92</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46103</v>
+        <v>46101</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -4359,14 +4359,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>PRIMEUR DE LA PLACE VILLE</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>-47.64</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>47.64</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46105</v>
+        <v>46103</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>-15.84</v>
+        <v>-23.61</v>
       </c>
       <c r="F61" t="n">
-        <v>15.84</v>
+        <v>23.61</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -4457,14 +4457,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>-157.98</v>
+        <v>-30.08</v>
       </c>
       <c r="F62" t="n">
-        <v>157.98</v>
+        <v>30.08</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4491,13 +4491,13 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>-33.16</v>
+        <v>-15.84</v>
       </c>
       <c r="F63" t="n">
-        <v>33.16</v>
+        <v>15.84</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -4555,14 +4555,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>-18.2</v>
+        <v>-157.98</v>
       </c>
       <c r="F64" t="n">
-        <v>18.2</v>
+        <v>157.98</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4589,13 +4589,13 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -4604,23 +4604,23 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>-15.76</v>
+        <v>-33.16</v>
       </c>
       <c r="F65" t="n">
-        <v>15.76</v>
+        <v>33.16</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4644,7 +4644,7 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>-36.37</v>
+        <v>-18.2</v>
       </c>
       <c r="F66" t="n">
-        <v>36.37</v>
+        <v>18.2</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46109</v>
+        <v>46107</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -4702,23 +4702,23 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>-149.68</v>
+        <v>-15.76</v>
       </c>
       <c r="F67" t="n">
-        <v>149.68</v>
+        <v>15.76</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4736,13 +4736,13 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -4751,14 +4751,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>BOUCHERIE DU MARCHE VILLE</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>-24.53</v>
+        <v>-36.37</v>
       </c>
       <c r="F68" t="n">
-        <v>24.53</v>
+        <v>36.37</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46110</v>
+        <v>46108</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -4800,23 +4800,23 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>-18.03</v>
+        <v>-9.92</v>
       </c>
       <c r="F69" t="n">
-        <v>18.03</v>
+        <v>9.92</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4840,7 +4840,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46115</v>
+        <v>46109</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -4849,14 +4849,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>-85.91</v>
+        <v>-149.68</v>
       </c>
       <c r="F70" t="n">
-        <v>85.91</v>
+        <v>149.68</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4879,17 +4879,17 @@
         </is>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46116</v>
+        <v>46109</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -4898,23 +4898,23 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>-59.32</v>
+        <v>-24.53</v>
       </c>
       <c r="F71" t="n">
-        <v>59.32</v>
+        <v>24.53</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4928,17 +4928,17 @@
         </is>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46116</v>
+        <v>46115</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -4947,23 +4947,23 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>-16.51</v>
+        <v>-85.91</v>
       </c>
       <c r="F72" t="n">
-        <v>16.51</v>
+        <v>85.91</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4987,7 +4987,7 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46118</v>
+        <v>46116</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -4996,23 +4996,23 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>-99.28</v>
+        <v>-59.32</v>
       </c>
       <c r="F73" t="n">
-        <v>99.28</v>
+        <v>59.32</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5036,7 +5036,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46119</v>
+        <v>46116</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -5045,23 +5045,23 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>-21.16</v>
+        <v>-16.51</v>
       </c>
       <c r="F74" t="n">
-        <v>21.16</v>
+        <v>16.51</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5085,7 +5085,7 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46120</v>
+        <v>46118</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -5094,23 +5094,23 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>-44.97</v>
+        <v>-99.28</v>
       </c>
       <c r="F75" t="n">
-        <v>44.97</v>
+        <v>99.28</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5134,7 +5134,7 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46120</v>
+        <v>46119</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -5143,23 +5143,23 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>-14.3</v>
+        <v>-21.16</v>
       </c>
       <c r="F76" t="n">
-        <v>14.3</v>
+        <v>21.16</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5183,7 +5183,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46122</v>
+        <v>46120</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -5192,23 +5192,23 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>-44.64</v>
+        <v>-44.97</v>
       </c>
       <c r="F77" t="n">
-        <v>44.64</v>
+        <v>44.97</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5226,13 +5226,13 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46122</v>
+        <v>46120</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>-39.74</v>
+        <v>-14.3</v>
       </c>
       <c r="F78" t="n">
-        <v>39.74</v>
+        <v>14.3</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46124</v>
+        <v>46122</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -5290,14 +5290,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PRIMEUR DE LA PLACE VILLE</t>
+          <t>BOUCHERIE DU MARCHE VILLE</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>-22.24</v>
+        <v>-44.64</v>
       </c>
       <c r="F79" t="n">
-        <v>22.24</v>
+        <v>44.64</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46126</v>
+        <v>46122</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -5339,23 +5339,23 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>-64.3</v>
+        <v>-39.74</v>
       </c>
       <c r="F80" t="n">
-        <v>64.3</v>
+        <v>39.74</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5373,13 +5373,13 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46128</v>
+        <v>46124</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>-20.8</v>
+        <v>-22.24</v>
       </c>
       <c r="F81" t="n">
-        <v>20.8</v>
+        <v>22.24</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46128</v>
+        <v>46126</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5437,23 +5437,23 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>-12.49</v>
+        <v>-64.3</v>
       </c>
       <c r="F82" t="n">
-        <v>12.49</v>
+        <v>64.3</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5471,13 +5471,13 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46131</v>
+        <v>46128</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -5486,23 +5486,23 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>PRIMEUR DE LA PLACE VILLE</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>-38.03</v>
+        <v>-20.8</v>
       </c>
       <c r="F83" t="n">
-        <v>38.03</v>
+        <v>20.8</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5526,7 +5526,7 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46133</v>
+        <v>46128</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -5535,14 +5535,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>-80.94</v>
+        <v>-12.49</v>
       </c>
       <c r="F84" t="n">
-        <v>80.94</v>
+        <v>12.49</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5575,7 +5575,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46133</v>
+        <v>46131</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -5584,23 +5584,23 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>-49.01</v>
+        <v>-38.03</v>
       </c>
       <c r="F85" t="n">
-        <v>49.01</v>
+        <v>38.03</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5624,7 +5624,7 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46134</v>
+        <v>46133</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -5633,14 +5633,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PRIMEUR DE LA PLACE VILLE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>-27.35</v>
+        <v>-80.94</v>
       </c>
       <c r="F86" t="n">
-        <v>27.35</v>
+        <v>80.94</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5673,7 +5673,7 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46135</v>
+        <v>46133</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -5682,14 +5682,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>BOUCHERIE DU MARCHE VILLE</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>-104.07</v>
+        <v>-49.01</v>
       </c>
       <c r="F87" t="n">
-        <v>104.07</v>
+        <v>49.01</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5722,7 +5722,7 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46135</v>
+        <v>46134</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -5731,23 +5731,23 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>PRIMEUR DE LA PLACE VILLE</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>-53.51</v>
+        <v>-27.35</v>
       </c>
       <c r="F88" t="n">
-        <v>53.51</v>
+        <v>27.35</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
@@ -5780,23 +5780,23 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>-51.39</v>
+        <v>-104.07</v>
       </c>
       <c r="F89" t="n">
-        <v>51.39</v>
+        <v>104.07</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5814,13 +5814,13 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46137</v>
+        <v>46135</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -5829,23 +5829,23 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>-74.64</v>
+        <v>-53.51</v>
       </c>
       <c r="F90" t="n">
-        <v>74.64</v>
+        <v>53.51</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5869,7 +5869,7 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46139</v>
+        <v>46135</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -5878,23 +5878,23 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>-130.24</v>
+        <v>-51.39</v>
       </c>
       <c r="F91" t="n">
-        <v>130.24</v>
+        <v>51.39</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5918,7 +5918,7 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46139</v>
+        <v>46137</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -5927,23 +5927,23 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>-79.92</v>
+        <v>-74.64</v>
       </c>
       <c r="F92" t="n">
-        <v>79.92</v>
+        <v>74.64</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5967,7 +5967,7 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46141</v>
+        <v>46139</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -5976,23 +5976,23 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>-36.67</v>
+        <v>-130.24</v>
       </c>
       <c r="F93" t="n">
-        <v>36.67</v>
+        <v>130.24</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6010,13 +6010,13 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -6025,23 +6025,23 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>-117.92</v>
+        <v>-79.92</v>
       </c>
       <c r="F94" t="n">
-        <v>117.92</v>
+        <v>79.92</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6065,7 +6065,7 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46144</v>
+        <v>46141</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -6074,23 +6074,23 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>-102.18</v>
+        <v>-36.67</v>
       </c>
       <c r="F95" t="n">
-        <v>102.18</v>
+        <v>36.67</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="P95" s="1" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46144</v>
+        <v>46142</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -6127,10 +6127,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>-63.85</v>
+        <v>-117.92</v>
       </c>
       <c r="F96" t="n">
-        <v>63.85</v>
+        <v>117.92</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="P96" s="1" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -6172,23 +6172,23 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>-35.27</v>
+        <v>-102.18</v>
       </c>
       <c r="F97" t="n">
-        <v>35.27</v>
+        <v>102.18</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6212,7 +6212,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46145</v>
+        <v>46144</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -6221,23 +6221,23 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>-43.6</v>
+        <v>-63.85</v>
       </c>
       <c r="F98" t="n">
-        <v>43.6</v>
+        <v>63.85</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6255,13 +6255,13 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46145</v>
+        <v>46144</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -6270,23 +6270,23 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>-30.49</v>
+        <v>-35.27</v>
       </c>
       <c r="F99" t="n">
-        <v>30.49</v>
+        <v>35.27</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6310,7 +6310,7 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46147</v>
+        <v>46145</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -6319,23 +6319,23 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>-45.9</v>
+        <v>-43.6</v>
       </c>
       <c r="F100" t="n">
-        <v>45.9</v>
+        <v>43.6</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6359,7 +6359,7 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46147</v>
+        <v>46145</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6368,23 +6368,23 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>-30.35</v>
+        <v>-30.49</v>
       </c>
       <c r="F101" t="n">
-        <v>30.35</v>
+        <v>30.49</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6408,7 +6408,7 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46149</v>
+        <v>46147</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -6417,23 +6417,23 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>-60.69</v>
+        <v>-45.9</v>
       </c>
       <c r="F102" t="n">
-        <v>60.69</v>
+        <v>45.9</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6451,13 +6451,13 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46150</v>
+        <v>46147</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -6466,14 +6466,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>-37.87</v>
+        <v>-30.35</v>
       </c>
       <c r="F103" t="n">
-        <v>37.87</v>
+        <v>30.35</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46152</v>
+        <v>46149</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -6515,23 +6515,23 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>-152.74</v>
+        <v>-60.69</v>
       </c>
       <c r="F104" t="n">
-        <v>152.74</v>
+        <v>60.69</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6555,7 +6555,7 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -6564,14 +6564,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
+          <t>BOUCHERIE DU MARCHE VILLE</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>-134.16</v>
+        <v>-37.87</v>
       </c>
       <c r="F105" t="n">
-        <v>134.16</v>
+        <v>37.87</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -6598,13 +6598,13 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46154</v>
+        <v>46152</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -6613,14 +6613,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>-94.75</v>
+        <v>-152.74</v>
       </c>
       <c r="F106" t="n">
-        <v>94.75</v>
+        <v>152.74</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6647,13 +6647,13 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>-92.34999999999999</v>
+        <v>-134.16</v>
       </c>
       <c r="F107" t="n">
-        <v>92.34999999999999</v>
+        <v>134.16</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -6711,23 +6711,23 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>-15.89</v>
+        <v>-92.34999999999999</v>
       </c>
       <c r="F108" t="n">
-        <v>15.89</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6745,13 +6745,13 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -6760,23 +6760,23 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>-24.28</v>
+        <v>-15.89</v>
       </c>
       <c r="F109" t="n">
-        <v>24.28</v>
+        <v>15.89</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6809,23 +6809,23 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>-19.16</v>
+        <v>-24.28</v>
       </c>
       <c r="F110" t="n">
-        <v>19.16</v>
+        <v>24.28</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6898,7 +6898,7 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -6907,23 +6907,23 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>-11.18</v>
+        <v>-60.28</v>
       </c>
       <c r="F112" t="n">
-        <v>11.18</v>
+        <v>60.28</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6941,13 +6941,13 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -6956,23 +6956,23 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>-70.12</v>
+        <v>-11.18</v>
       </c>
       <c r="F113" t="n">
-        <v>70.12</v>
+        <v>11.18</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6990,13 +6990,13 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>-85.5</v>
+        <v>-70.12</v>
       </c>
       <c r="F114" t="n">
-        <v>85.5</v>
+        <v>70.12</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -7054,23 +7054,23 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>-40.35</v>
+        <v>-85.5</v>
       </c>
       <c r="F115" t="n">
-        <v>40.35</v>
+        <v>85.5</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7088,13 +7088,13 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -7103,23 +7103,23 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>-38.51</v>
+        <v>-40.35</v>
       </c>
       <c r="F116" t="n">
-        <v>38.51</v>
+        <v>40.35</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7143,7 +7143,7 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -7152,23 +7152,23 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>BOUCHERIE DU MARCHE VILLE</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>-72.68000000000001</v>
+        <v>-38.51</v>
       </c>
       <c r="F117" t="n">
-        <v>72.68000000000001</v>
+        <v>38.51</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7186,13 +7186,13 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46173</v>
+        <v>46172</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -7201,23 +7201,23 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>-32.79</v>
+        <v>-72.68000000000001</v>
       </c>
       <c r="F118" t="n">
-        <v>32.79</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7235,13 +7235,13 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46174</v>
+        <v>46173</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -7250,14 +7250,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PRIMEUR DE LA PLACE VILLE</t>
+          <t>BOUCHERIE DU MARCHE VILLE</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>-18</v>
+        <v>-32.79</v>
       </c>
       <c r="F119" t="n">
-        <v>18</v>
+        <v>32.79</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="P119" s="1" t="n">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -7299,14 +7299,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
+          <t>PRIMEUR DE LA PLACE VILLE</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>-131.44</v>
+        <v>-18</v>
       </c>
       <c r="F120" t="n">
-        <v>131.44</v>
+        <v>18</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
@@ -7348,14 +7348,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PRIMEUR DE LA PLACE VILLE</t>
+          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>-24.56</v>
+        <v>-131.44</v>
       </c>
       <c r="F121" t="n">
-        <v>24.56</v>
+        <v>131.44</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -7382,13 +7382,13 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -7397,14 +7397,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>PRIMEUR DE LA PLACE VILLE</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>-17.94</v>
+        <v>-24.56</v>
       </c>
       <c r="F122" t="n">
-        <v>17.94</v>
+        <v>24.56</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -7446,14 +7446,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>-119.59</v>
+        <v>-17.94</v>
       </c>
       <c r="F123" t="n">
-        <v>119.59</v>
+        <v>17.94</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -7480,13 +7480,13 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46180</v>
+        <v>46178</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -7495,23 +7495,23 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>-38.19</v>
+        <v>-119.59</v>
       </c>
       <c r="F124" t="n">
-        <v>38.19</v>
+        <v>119.59</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7529,13 +7529,13 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46182</v>
+        <v>46180</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -7544,23 +7544,23 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>-26.36</v>
+        <v>-38.19</v>
       </c>
       <c r="F125" t="n">
-        <v>26.36</v>
+        <v>38.19</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7584,7 +7584,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -7593,23 +7593,23 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>BOUCHERIE DU MARCHE VILLE</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>-50.8</v>
+        <v>-26.36</v>
       </c>
       <c r="F126" t="n">
-        <v>50.8</v>
+        <v>26.36</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7627,13 +7627,13 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46186</v>
+        <v>46184</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -7646,10 +7646,10 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>-43.57</v>
+        <v>-50.8</v>
       </c>
       <c r="F127" t="n">
-        <v>43.57</v>
+        <v>50.8</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -7691,14 +7691,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PRIMEUR DE LA PLACE VILLE</t>
+          <t>BOUCHERIE DU MARCHE VILLE</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>-15.91</v>
+        <v>-47.64</v>
       </c>
       <c r="F128" t="n">
-        <v>15.91</v>
+        <v>47.64</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46189</v>
+        <v>46186</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -7744,10 +7744,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>-65.87</v>
+        <v>-43.57</v>
       </c>
       <c r="F129" t="n">
-        <v>65.87</v>
+        <v>43.57</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -7789,23 +7789,23 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>PRIMEUR DE LA PLACE VILLE</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>-32.19</v>
+        <v>-15.91</v>
       </c>
       <c r="F130" t="n">
-        <v>32.19</v>
+        <v>15.91</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7838,23 +7838,23 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>-17.42</v>
+        <v>-65.87</v>
       </c>
       <c r="F131" t="n">
-        <v>17.42</v>
+        <v>65.87</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7872,13 +7872,13 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -7887,23 +7887,23 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>-38.32</v>
+        <v>-32.19</v>
       </c>
       <c r="F132" t="n">
-        <v>38.32</v>
+        <v>32.19</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7927,7 +7927,7 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -7940,10 +7940,10 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>-20.1</v>
+        <v>-17.42</v>
       </c>
       <c r="F133" t="n">
-        <v>20.1</v>
+        <v>17.42</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46192</v>
+        <v>46190</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -7985,23 +7985,23 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>BOUCHERIE DU MARCHE VILLE</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>-21.14</v>
+        <v>-38.32</v>
       </c>
       <c r="F134" t="n">
-        <v>21.14</v>
+        <v>38.32</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8025,7 +8025,7 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46196</v>
+        <v>46190</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -8034,14 +8034,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>-35.76</v>
+        <v>-20.1</v>
       </c>
       <c r="F135" t="n">
-        <v>35.76</v>
+        <v>20.1</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8074,7 +8074,7 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46203</v>
+        <v>46192</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -8083,23 +8083,23 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>-57.22</v>
+        <v>-21.14</v>
       </c>
       <c r="F136" t="n">
-        <v>57.22</v>
+        <v>21.14</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8123,7 +8123,7 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46208</v>
+        <v>46196</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -8132,14 +8132,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>-16.59</v>
+        <v>-35.76</v>
       </c>
       <c r="F137" t="n">
-        <v>16.59</v>
+        <v>35.76</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="P137" s="1" t="n">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46210</v>
+        <v>46203</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -8181,14 +8181,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>-21.74</v>
+        <v>-57.22</v>
       </c>
       <c r="F138" t="n">
-        <v>21.74</v>
+        <v>57.22</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="P138" s="1" t="n">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46215</v>
+        <v>46208</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -8230,23 +8230,23 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>-79.72</v>
+        <v>-16.59</v>
       </c>
       <c r="F139" t="n">
-        <v>79.72</v>
+        <v>16.59</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8264,13 +8264,13 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46215</v>
+        <v>46210</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -8279,14 +8279,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>-44.31</v>
+        <v>-21.74</v>
       </c>
       <c r="F140" t="n">
-        <v>44.31</v>
+        <v>21.74</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46216</v>
+        <v>46215</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -8328,23 +8328,23 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>-15.2</v>
+        <v>-79.72</v>
       </c>
       <c r="F141" t="n">
-        <v>15.2</v>
+        <v>79.72</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8362,13 +8362,13 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46219</v>
+        <v>46215</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -8377,23 +8377,23 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>BOUCHERIE DU MARCHE VILLE</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>-33.92</v>
+        <v>-44.31</v>
       </c>
       <c r="F142" t="n">
-        <v>33.92</v>
+        <v>44.31</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8417,7 +8417,7 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46220</v>
+        <v>46216</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -8426,14 +8426,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PRIMEUR DE LA PLACE VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>-7.05</v>
+        <v>-15.2</v>
       </c>
       <c r="F143" t="n">
-        <v>7.05</v>
+        <v>15.2</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46221</v>
+        <v>46219</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -8475,23 +8475,23 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>-40.04</v>
+        <v>-33.92</v>
       </c>
       <c r="F144" t="n">
-        <v>40.04</v>
+        <v>33.92</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8515,7 +8515,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -8528,10 +8528,10 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>-24.67</v>
+        <v>-7.05</v>
       </c>
       <c r="F145" t="n">
-        <v>24.67</v>
+        <v>7.05</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46225</v>
+        <v>46221</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -8573,23 +8573,23 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>-142.19</v>
+        <v>-40.04</v>
       </c>
       <c r="F146" t="n">
-        <v>142.19</v>
+        <v>40.04</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8607,13 +8607,13 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -8622,14 +8622,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>PRIMEUR DE LA PLACE VILLE</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>-46.32</v>
+        <v>-24.67</v>
       </c>
       <c r="F147" t="n">
-        <v>46.32</v>
+        <v>24.67</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8662,7 +8662,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -8671,23 +8671,23 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>-23.51</v>
+        <v>-142.19</v>
       </c>
       <c r="F148" t="n">
-        <v>23.51</v>
+        <v>142.19</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8705,13 +8705,13 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -8720,14 +8720,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PRIMEUR DE LA PLACE VILLE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>-14.36</v>
+        <v>-46.32</v>
       </c>
       <c r="F149" t="n">
-        <v>14.36</v>
+        <v>46.32</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8760,7 +8760,7 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46229</v>
+        <v>46226</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -8769,23 +8769,23 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>-41.48</v>
+        <v>-23.51</v>
       </c>
       <c r="F150" t="n">
-        <v>41.48</v>
+        <v>23.51</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -8803,13 +8803,13 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46229</v>
+        <v>46227</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -8818,23 +8818,23 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>PRIMEUR DE LA PLACE VILLE</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>-40.46</v>
+        <v>-14.36</v>
       </c>
       <c r="F151" t="n">
-        <v>40.46</v>
+        <v>14.36</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -8867,23 +8867,23 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>-19.17</v>
+        <v>-41.48</v>
       </c>
       <c r="F152" t="n">
-        <v>19.17</v>
+        <v>41.48</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -8901,13 +8901,13 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46231</v>
+        <v>46229</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -8916,23 +8916,23 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>-50.63</v>
+        <v>-40.46</v>
       </c>
       <c r="F153" t="n">
-        <v>50.63</v>
+        <v>40.46</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -8956,7 +8956,7 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46232</v>
+        <v>46229</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -8969,10 +8969,10 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>-20.27</v>
+        <v>-19.17</v>
       </c>
       <c r="F154" t="n">
-        <v>20.27</v>
+        <v>19.17</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>-37.13</v>
+        <v>-50.63</v>
       </c>
       <c r="F155" t="n">
-        <v>37.13</v>
+        <v>50.63</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -9063,23 +9063,23 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>-21.01</v>
+        <v>-20.27</v>
       </c>
       <c r="F156" t="n">
-        <v>21.01</v>
+        <v>20.27</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9103,7 +9103,7 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -9112,23 +9112,23 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>BOUCHERIE DU MARCHE VILLE</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>-40.09</v>
+        <v>-37.13</v>
       </c>
       <c r="F157" t="n">
-        <v>40.09</v>
+        <v>37.13</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9152,7 +9152,7 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -9165,10 +9165,10 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>-28.82</v>
+        <v>-21.01</v>
       </c>
       <c r="F158" t="n">
-        <v>28.82</v>
+        <v>21.01</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -9210,23 +9210,23 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>-33.72</v>
+        <v>-40.09</v>
       </c>
       <c r="F159" t="n">
-        <v>33.72</v>
+        <v>40.09</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="P159" s="1" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46236</v>
+        <v>46234</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -9259,23 +9259,23 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>-32.34</v>
+        <v>-28.82</v>
       </c>
       <c r="F160" t="n">
-        <v>32.34</v>
+        <v>28.82</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="P160" s="1" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -9308,23 +9308,23 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>-42.18</v>
+        <v>-33.72</v>
       </c>
       <c r="F161" t="n">
-        <v>42.18</v>
+        <v>33.72</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -9348,7 +9348,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46239</v>
+        <v>46235</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -9357,14 +9357,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>-19.11</v>
+        <v>-18.43</v>
       </c>
       <c r="F162" t="n">
-        <v>19.11</v>
+        <v>18.43</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46242</v>
+        <v>46236</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -9406,23 +9406,23 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>-141.03</v>
+        <v>-32.34</v>
       </c>
       <c r="F163" t="n">
-        <v>141.03</v>
+        <v>32.34</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -9440,13 +9440,13 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46242</v>
+        <v>46238</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -9455,23 +9455,23 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>BOUCHERIE DU MARCHE VILLE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>-47.91</v>
+        <v>-42.18</v>
       </c>
       <c r="F164" t="n">
-        <v>47.91</v>
+        <v>42.18</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9495,7 +9495,7 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46242</v>
+        <v>46239</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -9504,23 +9504,23 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>BOUCHERIE DU MARCHE VILLE</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>-20.09</v>
+        <v>-19.11</v>
       </c>
       <c r="F165" t="n">
-        <v>20.09</v>
+        <v>19.11</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -9544,7 +9544,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -9553,14 +9553,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>SUPERMARCHE EXEMPLE CAMPAGNE</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>-114.02</v>
+        <v>-141.03</v>
       </c>
       <c r="F166" t="n">
-        <v>114.02</v>
+        <v>141.03</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -9587,13 +9587,13 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46245</v>
+        <v>46242</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -9602,14 +9602,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>BOUCHERIE DU MARCHE VILLE</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>-113.35</v>
+        <v>-47.91</v>
       </c>
       <c r="F167" t="n">
-        <v>113.35</v>
+        <v>47.91</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -9642,7 +9642,7 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46245</v>
+        <v>46242</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -9651,23 +9651,23 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>-24.36</v>
+        <v>-20.09</v>
       </c>
       <c r="F168" t="n">
-        <v>24.36</v>
+        <v>20.09</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -9691,7 +9691,7 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46247</v>
+        <v>46243</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -9700,23 +9700,23 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>-48.35</v>
+        <v>-114.02</v>
       </c>
       <c r="F169" t="n">
-        <v>48.35</v>
+        <v>114.02</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -9740,7 +9740,7 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46250</v>
+        <v>46245</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -9749,23 +9749,23 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>BRASSERIE DU COIN VILLE</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>-12.69</v>
+        <v>-113.35</v>
       </c>
       <c r="F170" t="n">
-        <v>12.69</v>
+        <v>113.35</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Restaurants et cafés</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -9789,7 +9789,7 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46253</v>
+        <v>46245</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -9798,23 +9798,23 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>-79.05</v>
+        <v>-24.36</v>
       </c>
       <c r="F171" t="n">
-        <v>79.05</v>
+        <v>24.36</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -9832,13 +9832,13 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46254</v>
+        <v>46249</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -9847,23 +9847,23 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>-33.79</v>
+        <v>-48.35</v>
       </c>
       <c r="F172" t="n">
-        <v>33.79</v>
+        <v>48.35</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -9887,7 +9887,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46256</v>
+        <v>46250</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -9896,23 +9896,23 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PHARMACIE CENTRALE VILLE</t>
+          <t>LIBRAIRIE DES ECOLES VILLE</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>-40.61</v>
+        <v>-12.69</v>
       </c>
       <c r="F173" t="n">
-        <v>40.61</v>
+        <v>12.69</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Santé</t>
+          <t>Culture et loisirs</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Soins et pharmacie</t>
+          <t>Livres, presse, sorties, jeux</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -9936,7 +9936,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46259</v>
+        <v>46253</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -9945,23 +9945,23 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PRIMEUR DE LA PLACE VILLE</t>
+          <t>STATION SERVICE CAMPAGNE</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>-25.49</v>
+        <v>-79.05</v>
       </c>
       <c r="F174" t="n">
-        <v>25.49</v>
+        <v>79.05</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Carburant et recharge</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -9979,13 +9979,13 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Campagne</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46259</v>
+        <v>46254</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -9994,14 +9994,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PRIMEUR DE LA PLACE VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>-22.9</v>
+        <v>-33.79</v>
       </c>
       <c r="F175" t="n">
-        <v>22.9</v>
+        <v>33.79</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46260</v>
+        <v>46256</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -10043,23 +10043,23 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>FROMAGERIE PERRET VILLE</t>
+          <t>PHARMACIE CENTRALE VILLE</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>-12.77</v>
+        <v>-40.61</v>
       </c>
       <c r="F176" t="n">
-        <v>12.77</v>
+        <v>40.61</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alimentation</t>
+          <t>Santé</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Soins et pharmacie</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -10083,7 +10083,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46261</v>
+        <v>46256</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -10092,14 +10092,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PRIMEUR DE LA PLACE VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>-23.4</v>
+        <v>-18.03</v>
       </c>
       <c r="F177" t="n">
-        <v>23.4</v>
+        <v>18.03</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46262</v>
+        <v>46259</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -10141,23 +10141,23 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>PRIMEUR DE LA PLACE VILLE</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>-14.77</v>
+        <v>-25.49</v>
       </c>
       <c r="F178" t="n">
-        <v>14.77</v>
+        <v>25.49</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -10181,7 +10181,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46263</v>
+        <v>46259</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -10190,14 +10190,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>BRASSERIE DU COIN VILLE</t>
+          <t>PRIMEUR DE LA PLACE VILLE</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>-76.92</v>
+        <v>-22.9</v>
       </c>
       <c r="F179" t="n">
-        <v>76.92</v>
+        <v>22.9</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Restaurants et cafés</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -10230,7 +10230,7 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46263</v>
+        <v>46260</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -10239,23 +10239,23 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>LIBRAIRIE DES ECOLES VILLE</t>
+          <t>FROMAGERIE PERRET VILLE</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>-29.65</v>
+        <v>-12.77</v>
       </c>
       <c r="F180" t="n">
-        <v>29.65</v>
+        <v>12.77</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Culture et loisirs</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Livres, presse, sorties, jeux</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -10279,7 +10279,7 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46264</v>
+        <v>46261</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -10288,23 +10288,23 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>STATION SERVICE CAMPAGNE</t>
+          <t>PRIMEUR DE LA PLACE VILLE</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>-60.28</v>
+        <v>-23.4</v>
       </c>
       <c r="F181" t="n">
-        <v>60.28</v>
+        <v>23.4</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Alimentation</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Carburant et recharge</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>Campagne</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
